--- a/Suivi_Formation_Fullstack_IA.xlsx
+++ b/Suivi_Formation_Fullstack_IA.xlsx
@@ -5,15 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asgri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asgri\Documents\Axis\fullstack-ia-formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D24C329-A7F4-4EBE-81DC-3D14DCC3162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1294E1-6E4A-474D-BBB4-106385072490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suivi" sheetId="1" r:id="rId1"/>
+    <sheet name="Module 0" sheetId="2" r:id="rId2"/>
+    <sheet name="Module 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Module 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Module 3" sheetId="5" r:id="rId5"/>
+    <sheet name="Module 4" sheetId="6" r:id="rId6"/>
+    <sheet name="Module 5" sheetId="7" r:id="rId7"/>
+    <sheet name="Module 6" sheetId="8" r:id="rId8"/>
+    <sheet name="Module 7" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
   <si>
     <t>Module</t>
   </si>
@@ -50,12 +58,6 @@
     <t>Module 0 – Introduction</t>
   </si>
   <si>
-    <t>Compte GitHub</t>
-  </si>
-  <si>
-    <t>Script Hello World JS</t>
-  </si>
-  <si>
     <t>Script Hello World Python</t>
   </si>
   <si>
@@ -165,13 +167,22 @@
   </si>
   <si>
     <t>Progression globale</t>
+  </si>
+  <si>
+    <t>TP Calculatirce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cours </t>
+  </si>
+  <si>
+    <t>C Programming for Beginners – freeCodeCamp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +194,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -202,7 +228,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -225,11 +251,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -240,12 +365,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,11 +372,75 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -268,6 +451,856 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR"/>
+              <a:t>Progression</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-EEB7-4324-98E3-2F423F442E0F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EEB7-4324-98E3-2F423F442E0F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-EEB7-4324-98E3-2F423F442E0F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Suivi!$C$1:$C$2</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EEB7-4324-98E3-2F423F442E0F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D462ADE4-9BF0-9263-FF46-CCE0703F93BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,21 +1607,233 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="3">
+        <f>AVERAGE(C19:C42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="13">
+        <f xml:space="preserve"> 'Module 0'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="14"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="15"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="17"/>
+      <c r="C22" s="13">
+        <f>'Module 1'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="18"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="15"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="13">
+        <f>'Module 2'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="14"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="15"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="13">
+        <f>'Module 3'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="14"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="15"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="13">
+        <f>'Module 4'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="15"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="13">
+        <f>'Module 5'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="14"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="15"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="13">
+        <f>'Module 6'!E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="14"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="15"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="13">
+        <f>'Module 7'!E5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="14"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="A34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="A28:B30"/>
+    <mergeCell ref="A40:B42"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C19:C21">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CFC5B1-1A26-4CD9-A33E-5E4E4D75B70F}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -600,40 +1845,655 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="E2:E5"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://www.youtube.com/watch?v=KJgsSFOSQv0" xr:uid="{0E8590AE-67CF-4A42-9E05-7FF68C8C722B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB689B-155E-4500-A0DC-CBC030884A95}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="D2" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E2:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EE5B77-E39E-4DAC-A4C3-E7FAEF2C4519}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F98AC4-D8FD-4289-8E6B-9F72B8F26FE9}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB5D7F1-3A4A-46EA-BD4D-08696B995DF3}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375B622C-1934-46BC-82CF-D48FAF7FDEAE}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EE061E-F1C8-46ED-A395-A37D5E771A68}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3">
+        <f>COUNTIF(D2:D5, TRUE)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57B4310-D4F8-44AA-9613-16B72E4C5BA1}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
@@ -641,380 +2501,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3">
-        <f>COUNTIF(D7:D10, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3">
-        <f>COUNTIF(D13:D16, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3">
-        <f>COUNTIF(D19:D22, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="3">
-        <f>COUNTIF(D25:D28, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="3">
-        <f>COUNTIF(D31:D34, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="3">
-        <f>COUNTIF(D37:D40, TRUE)/4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="3">
-        <f>COUNTIF(D43:D45, TRUE)/3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" s="3">
-        <f>AVERAGE(E5,E11,E17,E23,E29,E35,E41,E46)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A25:B28"/>
-    <mergeCell ref="A31:B34"/>
-    <mergeCell ref="A37:B40"/>
-    <mergeCell ref="A43:B45"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B4"/>
-    <mergeCell ref="A7:B10"/>
-    <mergeCell ref="A13:B16"/>
-    <mergeCell ref="A19:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Suivi_Formation_Fullstack_IA.xlsx
+++ b/Suivi_Formation_Fullstack_IA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asgri\Documents\Axis\fullstack-ia-formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1294E1-6E4A-474D-BBB4-106385072490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A10049-94DB-4C96-BDF5-651C2FCE060E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>Module</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Module 0 – Introduction</t>
   </si>
   <si>
-    <t>Script Hello World Python</t>
-  </si>
-  <si>
     <t>Progression</t>
   </si>
   <si>
@@ -169,20 +166,46 @@
     <t>Progression globale</t>
   </si>
   <si>
-    <t>TP Calculatirce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cours </t>
-  </si>
-  <si>
-    <t>C Programming for Beginners – freeCodeCamp</t>
+    <t>VSCode installé</t>
+  </si>
+  <si>
+    <t>Script Hello World</t>
+  </si>
+  <si>
+    <t>Terminal utilisé (3 commandes)</t>
+  </si>
+  <si>
+    <t>Dépôt GitHub à jour</t>
+  </si>
+  <si>
+    <t>"Certification" FreeCodeCamp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TP.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fonctionnel</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,19 +222,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -228,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -350,11 +370,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -372,15 +405,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -388,16 +412,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -405,6 +420,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -424,6 +442,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1608,7 +1647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
@@ -1617,182 +1656,188 @@
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="3">
         <f>AVERAGE(C19:C42)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C2" s="12">
+    <row r="2" spans="1:3">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="13">
-        <f xml:space="preserve"> 'Module 0'!E6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="14"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="15"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="13">
+      <c r="B19" s="10"/>
+      <c r="C19" s="7">
+        <f xml:space="preserve"> 'Module 0'!E8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="7">
         <f>'Module 1'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="14"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="15"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="13">
+    <row r="23" spans="1:3">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="7">
         <f>'Module 2'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="14"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="15"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="13">
+    <row r="26" spans="1:3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="7">
         <f>'Module 3'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="14"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="15"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="13">
+    <row r="29" spans="1:3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="7">
         <f>'Module 4'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="14"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="15"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="13">
+    <row r="32" spans="1:3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="8"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="9"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="7">
         <f>'Module 5'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="14"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="15"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="13">
+    <row r="35" spans="1:3">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="8"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="7">
         <f>'Module 6'!E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="14"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="15"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="13">
+    <row r="38" spans="1:3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="8"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="9"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="7">
         <f>'Module 7'!E5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="14"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="15"/>
+    <row r="41" spans="1:3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="8"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A19:B21"/>
     <mergeCell ref="C40:C42"/>
     <mergeCell ref="C28:C30"/>
     <mergeCell ref="A31:B33"/>
@@ -1801,12 +1846,6 @@
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="A37:B39"/>
     <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A19:B21"/>
     <mergeCell ref="A28:B30"/>
     <mergeCell ref="A40:B42"/>
   </mergeCells>
@@ -1822,18 +1861,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CFC5B1-1A26-4CD9-A33E-5E4E4D75B70F}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1844,57 +1883,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="23"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5" t="s">
+      <c r="D4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3">
-        <f>COUNTIF(D2:D5, TRUE)/4</f>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3">
+        <f>COUNTIF(D2:D7, TRUE)/6</f>
         <v>0</v>
       </c>
     </row>
@@ -1902,11 +1959,8 @@
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B4"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E2:E7"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://www.youtube.com/watch?v=KJgsSFOSQv0" xr:uid="{0E8590AE-67CF-4A42-9E05-7FF68C8C722B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1914,18 +1968,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB689B-155E-4500-A0DC-CBC030884A95}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1936,55 +1990,55 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2005,18 +2059,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EE5B77-E39E-4DAC-A4C3-E7FAEF2C4519}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2027,51 +2081,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2091,18 +2145,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F98AC4-D8FD-4289-8E6B-9F72B8F26FE9}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2113,51 +2167,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2177,18 +2231,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB5D7F1-3A4A-46EA-BD4D-08696B995DF3}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2199,51 +2253,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2263,7 +2317,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375B622C-1934-46BC-82CF-D48FAF7FDEAE}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -2271,11 +2325,11 @@
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2286,51 +2340,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2350,7 +2404,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EE061E-F1C8-46ED-A395-A37D5E771A68}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -2358,11 +2412,11 @@
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2373,51 +2427,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3">
@@ -2437,18 +2491,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57B4310-D4F8-44AA-9613-16B72E4C5BA1}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
+    <row r="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2459,41 +2513,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D4" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3">

--- a/Suivi_Formation_Fullstack_IA.xlsx
+++ b/Suivi_Formation_Fullstack_IA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asgri\Documents\Axis\fullstack-ia-formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A10049-94DB-4C96-BDF5-651C2FCE060E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711A8C0A-161E-42A7-96AD-5E303422CDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suivi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>Module</t>
   </si>
@@ -62,18 +62,6 @@
   </si>
   <si>
     <t>Module 1 – Frontend</t>
-  </si>
-  <si>
-    <t>HTML/CSS</t>
-  </si>
-  <si>
-    <t>JS DOM</t>
-  </si>
-  <si>
-    <t>React Intro</t>
-  </si>
-  <si>
-    <t>Mini-portfolio</t>
   </si>
   <si>
     <t>Module 2 – Backend</t>
@@ -200,12 +188,66 @@
       <t xml:space="preserve"> fonctionnel</t>
     </r>
   </si>
+  <si>
+    <t>Introduction à Bootstrap</t>
+  </si>
+  <si>
+    <t>Sass Variables &amp; Nesting</t>
+  </si>
+  <si>
+    <t>Bootstrap Grid</t>
+  </si>
+  <si>
+    <t>Bootstrap Components</t>
+  </si>
+  <si>
+    <t>jQuery Selectors</t>
+  </si>
+  <si>
+    <t>jQuery Events &amp; Effects</t>
+  </si>
+  <si>
+    <t>Sass Partials &amp; Mixins</t>
+  </si>
+  <si>
+    <t>React Components</t>
+  </si>
+  <si>
+    <t>JSX &amp; Props</t>
+  </si>
+  <si>
+    <t>State &amp; Lifecycle</t>
+  </si>
+  <si>
+    <t>Introduction à Redux</t>
+  </si>
+  <si>
+    <t>Actions, Reducers, Store</t>
+  </si>
+  <si>
+    <t>Connecter React &amp; Redux</t>
+  </si>
+  <si>
+    <t>Projet 1: Random Quote Machine</t>
+  </si>
+  <si>
+    <t>Projet 2: Markdown Previewer</t>
+  </si>
+  <si>
+    <t>Projet 3: Drum Machine</t>
+  </si>
+  <si>
+    <t>Projet 4: JavaScript Calculator</t>
+  </si>
+  <si>
+    <t>Projet 5: 25 + 5 Clock</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +274,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -413,6 +463,9 @@
       </extLst>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,9 +473,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -443,26 +493,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1658,7 +1713,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C1" s="3">
         <f>AVERAGE(C19:C42)</f>
@@ -1671,173 +1726,167 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="7">
+      <c r="B19" s="17"/>
+      <c r="C19" s="8">
         <f xml:space="preserve"> 'Module 0'!E8</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="7">
-        <f>'Module 1'!E6</f>
+      <c r="C22" s="8">
+        <f>'Module 1'!E20</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="9"/>
+      <c r="C24" s="10"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="7">
+      <c r="A25" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="8">
         <f>'Module 2'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="7">
+      <c r="A28" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="8">
         <f>'Module 3'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="7">
+      <c r="A31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="8">
         <f>'Module 4'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="8"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="9"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="7">
+      <c r="A34" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="8">
         <f>'Module 5'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="8"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="9"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="10"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="7">
+      <c r="A37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="8">
         <f>'Module 6'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="8"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="9"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="9"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="10"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="7">
+      <c r="A40" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="8">
         <f>'Module 7'!E5</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="8"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="9"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="9"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A19:B21"/>
     <mergeCell ref="C40:C42"/>
     <mergeCell ref="C28:C30"/>
     <mergeCell ref="A31:B33"/>
@@ -1848,6 +1897,12 @@
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="A28:B30"/>
     <mergeCell ref="A40:B42"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A19:B21"/>
   </mergeCells>
   <conditionalFormatting sqref="C19:C21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -1869,10 +1924,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1884,66 +1939,66 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
+      <c r="D5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="23"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="C5" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="23"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="C6" s="22" t="s">
-        <v>46</v>
-      </c>
       <c r="D6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="C7" s="22" t="s">
-        <v>44</v>
+      <c r="C7" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="D7" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5">
       <c r="C8" s="2" t="s">
@@ -1967,19 +2022,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB689B-155E-4500-A0DC-CBC030884A95}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+    <row r="1" spans="1:19">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1990,67 +2045,302 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:19">
+      <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="18"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+        <v>43</v>
+      </c>
+      <c r="D2" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="17"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="D3" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="17"/>
+      <c r="B4" s="19"/>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="19"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="D4" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="17"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="b">
+        <v>47</v>
+      </c>
+      <c r="D5" s="23" t="b">
         <v>0</v>
       </c>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:19">
       <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="C13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+    </row>
+    <row r="17" spans="3:19">
+      <c r="C17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+    </row>
+    <row r="18" spans="3:19">
+      <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+    </row>
+    <row r="19" spans="3:19">
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+    </row>
+    <row r="20" spans="3:19">
+      <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3">
-        <f>COUNTIF(D2:D5, TRUE)/4</f>
-        <v>0</v>
-      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3">
+        <f>COUNTIF(D2:D19, TRUE)/(19-2)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+    </row>
+    <row r="21" spans="3:19">
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+    </row>
+    <row r="22" spans="3:19">
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+    </row>
+    <row r="23" spans="3:19">
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
+    </row>
+    <row r="24" spans="3:19">
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+    </row>
+    <row r="25" spans="3:19">
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+    </row>
+    <row r="26" spans="3:19">
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+    </row>
+    <row r="27" spans="3:19">
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:B5"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E2:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2067,10 +2357,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2082,46 +2372,50 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
@@ -2134,9 +2428,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B5"/>
+    <mergeCell ref="E2:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2153,10 +2448,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2168,42 +2463,42 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
@@ -2239,10 +2534,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2254,42 +2549,42 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
@@ -2326,10 +2621,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2341,42 +2636,42 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
@@ -2413,10 +2708,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2428,42 +2723,42 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
@@ -2499,10 +2794,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2514,32 +2809,32 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="10"/>
+      <c r="A2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="17"/>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>0</v>

--- a/Suivi_Formation_Fullstack_IA.xlsx
+++ b/Suivi_Formation_Fullstack_IA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asgri\Documents\Axis\fullstack-ia-formation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YohannGUILLOUX\Documents\GitHub\fullstack-ia-formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711A8C0A-161E-42A7-96AD-5E303422CDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94846600-9902-4759-8AF7-C90D121D02B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suivi" sheetId="1" r:id="rId1"/>
@@ -466,6 +466,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -473,6 +487,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -493,9 +510,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -504,20 +518,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,7 +727,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>6.25E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -1702,13 +1702,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C1" s="3">
         <f>AVERAGE(C19:C42)</f>
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1726,167 +1726,173 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="8">
+      <c r="B19" s="14"/>
+      <c r="C19" s="11">
         <f xml:space="preserve"> 'Module 0'!E8</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="12"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="10"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="13"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8">
+      <c r="B22" s="16"/>
+      <c r="C22" s="11">
         <f>'Module 1'!E20</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="12"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="10"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="8">
+      <c r="B25" s="14"/>
+      <c r="C25" s="11">
         <f>'Module 2'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="12"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="10"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="8">
+      <c r="B28" s="14"/>
+      <c r="C28" s="11">
         <f>'Module 3'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="12"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="13"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="8">
+      <c r="B31" s="14"/>
+      <c r="C31" s="11">
         <f>'Module 4'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="9"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="12"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="13"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="8">
+      <c r="B34" s="14"/>
+      <c r="C34" s="11">
         <f>'Module 5'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="9"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="12"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="10"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="13"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="8">
+      <c r="B37" s="14"/>
+      <c r="C37" s="11">
         <f>'Module 6'!E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="9"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="12"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="10"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="13"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="8">
+      <c r="B40" s="14"/>
+      <c r="C40" s="11">
         <f>'Module 7'!E5</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="9"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="12"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="10"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="A19:B21"/>
     <mergeCell ref="C40:C42"/>
     <mergeCell ref="C28:C30"/>
     <mergeCell ref="A31:B33"/>
@@ -1897,12 +1903,6 @@
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="A28:B30"/>
     <mergeCell ref="A40:B42"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="A19:B21"/>
   </mergeCells>
   <conditionalFormatting sqref="C19:C21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -1917,17 +1917,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CFC5B1-1A26-4CD9-A33E-5E4E4D75B70F}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1939,39 +1939,39 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="19"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5">
       <c r="C5" s="7" t="s">
@@ -1980,7 +1980,7 @@
       <c r="D5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="7" t="s">
@@ -1989,7 +1989,7 @@
       <c r="D6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5">
       <c r="C7" s="7" t="s">
@@ -1998,7 +1998,7 @@
       <c r="D7" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5">
       <c r="C8" s="2" t="s">
@@ -2007,7 +2007,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3">
         <f>COUNTIF(D2:D7, TRUE)/6</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2023,18 +2023,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCB689B-155E-4500-A0DC-CBC030884A95}">
   <dimension ref="A1:S27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2046,231 +2046,231 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="20"/>
+      <c r="D2" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="17"/>
-      <c r="B3" s="19"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="20"/>
+      <c r="D3" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="17"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="20"/>
+      <c r="D4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="20"/>
+      <c r="D5" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:19">
       <c r="C6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="20"/>
+      <c r="D6" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:19">
       <c r="C7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="20"/>
+      <c r="D7" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:19">
       <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20"/>
+      <c r="D8" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:19">
       <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
+      <c r="D9" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
     </row>
     <row r="10" spans="1:19">
       <c r="C10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="20"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
+      <c r="D10" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
     </row>
     <row r="11" spans="1:19">
       <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
+      <c r="D11" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
     </row>
     <row r="12" spans="1:19">
       <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="20"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
+      <c r="D12" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
     </row>
     <row r="13" spans="1:19">
       <c r="C13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
+      <c r="D13" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
     </row>
     <row r="14" spans="1:19">
       <c r="C14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
+      <c r="D14" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="23"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
     </row>
     <row r="15" spans="1:19">
       <c r="C15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
+      <c r="D15" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
     </row>
     <row r="16" spans="1:19">
       <c r="C16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
+      <c r="D16" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
     </row>
     <row r="17" spans="3:19">
       <c r="C17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
+      <c r="D17" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="23"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
     </row>
     <row r="18" spans="3:19">
       <c r="C18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
+      <c r="D18" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
     </row>
     <row r="19" spans="3:19">
       <c r="C19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
+      <c r="D19" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
     </row>
     <row r="20" spans="3:19">
       <c r="C20" s="2" t="s">
@@ -2281,60 +2281,60 @@
         <f>COUNTIF(D2:D19, TRUE)/(19-2)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
     </row>
     <row r="21" spans="3:19">
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
     </row>
     <row r="22" spans="3:19">
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
     </row>
     <row r="23" spans="3:19">
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
     </row>
     <row r="24" spans="3:19">
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
     </row>
     <row r="25" spans="3:19">
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
     </row>
     <row r="26" spans="3:19">
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
     </row>
     <row r="27" spans="3:19">
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2349,18 +2349,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65EE5B77-E39E-4DAC-A4C3-E7FAEF2C4519}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2372,50 +2372,50 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="20"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5">
       <c r="C6" s="2" t="s">
@@ -2440,18 +2440,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F98AC4-D8FD-4289-8E6B-9F72B8F26FE9}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2463,10 +2463,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
@@ -2475,8 +2475,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2485,8 +2485,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
@@ -2495,8 +2495,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
@@ -2526,18 +2526,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB5D7F1-3A4A-46EA-BD4D-08696B995DF3}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2549,10 +2549,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
@@ -2561,8 +2561,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
@@ -2571,8 +2571,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2581,8 +2581,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
@@ -2612,19 +2612,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375B622C-1934-46BC-82CF-D48FAF7FDEAE}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2636,10 +2636,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
@@ -2648,8 +2648,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>24</v>
       </c>
@@ -2658,8 +2658,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
@@ -2668,8 +2668,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
@@ -2699,19 +2699,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EE061E-F1C8-46ED-A395-A37D5E771A68}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2723,10 +2723,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
@@ -2735,8 +2735,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
@@ -2745,8 +2745,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
@@ -2755,8 +2755,8 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
@@ -2786,18 +2786,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57B4310-D4F8-44AA-9613-16B72E4C5BA1}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2809,10 +2809,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
@@ -2821,8 +2821,8 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
@@ -2831,8 +2831,8 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
